--- a/output/tables/QC/finished_tables/temp2.HWE.p_adjust.xlsx
+++ b/output/tables/QC/finished_tables/temp2.HWE.p_adjust.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\R_WD\revised_bison_popgen\output\tables\QC\finished_tables\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\D_RWD\revised_bison_popgen\output\tables\QC\finished_tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85D0F0D6-39DA-424F-9FF5-97C32398317E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC86B2EF-6CCC-49A2-A7DF-9C9D760FA2DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-118" yWindow="-118" windowWidth="20343" windowHeight="12934" xr2:uid="{A919F78D-9AD9-49EE-90A8-63E021EA3445}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A919F78D-9AD9-49EE-90A8-63E021EA3445}"/>
   </bookViews>
   <sheets>
     <sheet name="temp2_v3.HWE.p_adjust" sheetId="1" r:id="rId1"/>
@@ -1138,19 +1138,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47553EA4-5AB1-4B57-8320-6FC2C7D3F85C}">
   <dimension ref="A1:R50"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.109375" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="4" width="7" style="5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.21875" style="5" bestFit="1" customWidth="1"/>
-    <col min="6" max="11" width="7" style="5" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="5.33203125" style="5" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.5546875" style="5" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.44140625" style="5" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="9.21875" style="5" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="10.44140625" style="5" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="6.44140625" style="5" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="8.88671875" style="3"/>
+    <col min="1" max="1" width="9.85546875" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="7" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.42578125" style="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="6" max="9" width="7" style="5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.42578125" style="5" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7" style="5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.5703125" style="5" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.7109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="10.42578125" style="5" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="11.85546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="7.42578125" style="5" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="8.85546875" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
